--- a/全Lora.xlsx
+++ b/全Lora.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="14130" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="氛围" sheetId="4" r:id="rId1"/>
@@ -17,26 +17,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">角色!$A$1:$G$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Pony角色!$A$1:$F$54</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="1161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="1175">
   <si>
     <t>氛围Lora列表</t>
   </si>
@@ -2118,94 +2106,136 @@
     <t>DakiV4, long hair,((black hair)), hair ornament,</t>
   </si>
   <si>
-    <t>PonyChar/Rem.safetensors</t>
-  </si>
-  <si>
-    <t>Rem, blue hair,</t>
-  </si>
-  <si>
-    <t>PonyChar/jingliuponyxl4.safetensors</t>
-  </si>
-  <si>
-    <t>jingliu \(honkai: star rail\)</t>
-  </si>
-  <si>
-    <t>PonyChar/fuxuan-strPO-v1b.safetensors</t>
+    <t>ram</t>
+  </si>
+  <si>
+    <t>PonyChar\rezero-ram-ponyxl-lora-nochekaiser.safetensors</t>
+  </si>
+  <si>
+    <t>ram, hair flower, hair ornament, hair over one eye, (pink hair), red eyes, short hair, x hair ornament, pink hair</t>
+  </si>
+  <si>
+    <t>PonyChar\rezero-rem-ponyxl-lora-nochekaiser.safetensors</t>
+  </si>
+  <si>
+    <t>rem, blue eyes, (blue hair), hair ornament, hair over one eye, hair ribbon, short hair, x hair ornament, blue hair,</t>
+  </si>
+  <si>
+    <t>PonyChar\star_rail_all_v2.safetensors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1girl, jingliu_\(honkai:_star_rail\), red_eyes, long_hair, (white_hair), bare_shoulders, high_ponytail,  hair_between_eyes, </t>
   </si>
   <si>
     <t>fuxuan, white pantyhose, high heels</t>
   </si>
   <si>
-    <t>PonyChar/march7thponyxl3.safetensors</t>
-  </si>
-  <si>
     <t>march 7th \(honkai: star rail\)</t>
   </si>
   <si>
-    <t>PonyChar/kafka_1k_pony.safetensors</t>
-  </si>
-  <si>
-    <t>1girl, kafka_\(honkai:_star_rail\), eyewear_on_head, sunglasses, large_breasts, round_eyewear,</t>
-  </si>
-  <si>
-    <t>PonyChar/qingqueponyxl-10.safetensors</t>
+    <t xml:space="preserve">1girl, kafka_\(honkai:_star_rail\), (purple_hair), purple_eyes, long_hair, eyewear_on_head, large_breasts, sunglasses, </t>
   </si>
   <si>
     <t>qingque \(honkai: star rail\)</t>
   </si>
   <si>
-    <t>PonyChar/silverwolfponyxl.safetensors</t>
-  </si>
-  <si>
     <t>silver wolf \(honkai: star rail\)</t>
   </si>
   <si>
-    <t>PonyChar/astaponyxl1.safetensors</t>
-  </si>
-  <si>
     <t>asta \(honkai: star rail\)</t>
   </si>
   <si>
-    <t>PonyChar/seeleponyxl.safetensors</t>
-  </si>
-  <si>
     <t>seele \(honkai: star rail\)</t>
   </si>
   <si>
-    <t>PonyChar/himekoponyxl2.safetensors</t>
-  </si>
-  <si>
     <t>himeko \(honkai: star rail\)</t>
   </si>
   <si>
-    <t>PonyChar/kanroji_mitsuri_pdxl_goofy.safetensors</t>
-  </si>
-  <si>
-    <t>kanroji-mitsuri,green eyes, multicolored hair, twin_braids</t>
-  </si>
-  <si>
-    <t>PonyChar/shinobu-kochou-ponyxl-lora-nochekaiser.safetensors</t>
-  </si>
-  <si>
-    <t>shinobu kochou,  black hair, butterfly, butterfly hair ornament, butterfly print,  gradient hair, hair ornament, multicolored hair, parted bangs, purple hair, short hair, two-tone hair,</t>
-  </si>
-  <si>
-    <t>PonyChar/NezukoPony_v2.safetensors</t>
-  </si>
-  <si>
-    <t>kamado nezuko,1girl, black hair, pink eyes, magenta pupils, pink hair ribbon, two-tone hair</t>
-  </si>
-  <si>
-    <t>PonyChar/uta_(one_piece).safetensors</t>
+    <t>PonyChar\mitsuri-kanroji-anime-ponyxl-lora-nochekaiser.safetensors</t>
+  </si>
+  <si>
+    <t>mitsuri kanroji, braid, gradient hair, green eyes, (green hair), long hair, mole, mole under eye, multicolored hair, pink hair, twin braids, two-tone hair,</t>
+  </si>
+  <si>
+    <t>PonyChar\shinobu-kochou-anime-ponyxl-lora-nochekaiser.safetensors</t>
+  </si>
+  <si>
+    <t>shinobu kochou, animal print, black hair, butterfly, butterfly hair ornament, butterfly print, forehead, gradient hair, hair ornament, multicolored hair, parted bangs, (purple hair), short hair, two-tone hair,</t>
+  </si>
+  <si>
+    <t>PonyChar\Nezuko Kamado - Pony.safetensors</t>
+  </si>
+  <si>
+    <t>aNezuko,long hair,(black hair),pink eyes,bit gag,bamboo gag,pink kimono</t>
   </si>
   <si>
     <t>,uta_\(one_piece\),</t>
   </si>
   <si>
-    <t>PonyChar/Char-Genshin-Furina-Pony-V1.safetensors</t>
+    <t>PonyChar\Boa_hancock.safetensors</t>
+  </si>
+  <si>
+    <t>Boa_hancock, (black hair),</t>
+  </si>
+  <si>
+    <t>PonyChar\Hinata_Pony.safetensors</t>
+  </si>
+  <si>
+    <t>(hinata, hyuuga hinata, purple eyes, blunt bangs, (black hair), white eyes, no pupils</t>
+  </si>
+  <si>
+    <t>PonyChar\genshin_v4.safetensors</t>
+  </si>
+  <si>
+    <t>1girl, kamisato_ayaka_\(heytea\), genshin_impact, ponytail, mole_under_eye, white_sailor_collar,  tress_ribbon, hair_bow, blunt_tresses,(blue hair),</t>
+  </si>
+  <si>
+    <t>yae_miko, 1girl, genshin_impact, large_breasts, (pink hair)</t>
+  </si>
+  <si>
+    <t>ganyu_\(genshin_impact\), 1girl, neck_bell, bare_shoulders, bodystocking, (blue hair),</t>
+  </si>
+  <si>
+    <t>1girl, hu_tao_\(genshin_impact\), flower-shaped_pupils, black_nails, boo_tao_\(genshin_impact\), black_headwear, hat_flower,nail_polish, thighs, (black hair),</t>
+  </si>
+  <si>
+    <t>shenhe_\(genshin_impact\), 1girl, blue_eyes, hair_over_one_eye, (white_hair), large_breasts, hair_ornament, long_hair, very_long_hair, (grey_hair),  tassel_earrings</t>
+  </si>
+  <si>
+    <t>1girl, raiden_shogun, genshin_impact, mole_under_eye, cleavage, large_breasts, purple_kimono,  long_braid, purple_nails, (blue hair)</t>
+  </si>
+  <si>
+    <t>keqing_\(genshin_impact\), 1girl, bare_shoulders, thighs, large_breasts, black_pantyhose, cleavage, (purple hair)</t>
+  </si>
+  <si>
+    <t>1girl, yoimiya_\(genshin_impact\),  arm_tattoo, ponytail, cleavage,  bandaged_leg, chest_tattoo, bandaged_arm,(yellow hair),</t>
+  </si>
+  <si>
+    <t>1girl, nahida_\(genshin_impact\), pointy_ears, side_ponytail, (green hair)</t>
+  </si>
+  <si>
+    <t>ningguang_\(genshin_impact\), 1girl, hair_stick, large_breasts, (white_hair),  bare_shoulders, red_eyes, elbow_gloves,  long_hair, sitting, tassel_hair_ornament</t>
   </si>
   <si>
     <t>furina \(genshin impact\)</t>
+  </si>
+  <si>
+    <t>千织</t>
+  </si>
+  <si>
+    <t>1girl, chiori_\(genshin_impact\),  side_ponytail, hair_stick, black_pantyhose, bare_shoulders, (brown hair)</t>
+  </si>
+  <si>
+    <t>时崎狂三</t>
+  </si>
+  <si>
+    <t>PonyChar\kurumi-tokisaki-booru-ponyxl-lora-nochekaiser.safetensors</t>
+  </si>
+  <si>
+    <t>kurumi tokisaki, (black hair), red eyes, long hair,</t>
+  </si>
+  <si>
+    <t>Date A Live</t>
   </si>
   <si>
     <t>动作Lora列表</t>
@@ -2956,7 +2986,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="0" tint="-0.0499893185216834"/>
-        <rFont val="宋体"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -2967,7 +2997,7 @@
         <b/>
         <sz val="11"/>
         <color theme="0" tint="-0.0499893185216834"/>
-        <rFont val="宋体"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -3582,7 +3612,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -3593,21 +3623,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.349986266670736"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.0499893185216834"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3615,7 +3645,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3623,7 +3653,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3631,14 +3661,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3646,7 +3676,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3654,7 +3684,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3662,7 +3692,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3670,7 +3700,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3678,14 +3708,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3693,7 +3723,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3701,7 +3731,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3709,14 +3739,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3724,42 +3754,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -3767,7 +3797,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0" tint="-0.0499893185216834"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -4288,55 +4318,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="18">
     <dxf>
@@ -4590,8 +4620,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24251920" y="8915400"/>
-          <a:ext cx="2420620" cy="171450"/>
+          <a:off x="21222335" y="8001000"/>
+          <a:ext cx="2118360" cy="190500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5000,7 +5030,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B142"/>
-  <sheetFormatPr defaultColWidth="39.6666666666667" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="39.6666666666667" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="39.6666666666667" style="2" customWidth="1"/>
     <col min="2" max="16384" width="39.6666666666667" style="2"/>
@@ -5019,7 +5049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="40.5" spans="1:2">
+    <row r="3" ht="45" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5027,7 +5057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="40.5" spans="1:2">
+    <row r="4" ht="30" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -5035,7 +5065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" ht="40.5" spans="1:2">
+    <row r="5" ht="45" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -5043,7 +5073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="40.5" spans="1:2">
+    <row r="6" ht="45" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -5051,7 +5081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="40.5" spans="1:2">
+    <row r="7" ht="45" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -5059,7 +5089,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" ht="40.5" spans="1:2">
+    <row r="8" ht="45" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -5067,7 +5097,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" ht="40.5" spans="1:2">
+    <row r="9" ht="45" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -5075,7 +5105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="40.5" spans="1:2">
+    <row r="10" ht="45" spans="1:2">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -5083,7 +5113,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="40.5" spans="1:2">
+    <row r="11" ht="45" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -5091,7 +5121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" ht="40.5" spans="1:2">
+    <row r="12" ht="30" spans="1:2">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -5099,7 +5129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="40.5" spans="1:2">
+    <row r="13" ht="30" spans="1:2">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -5107,7 +5137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" ht="40.5" spans="1:2">
+    <row r="14" ht="30" spans="1:2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -5115,7 +5145,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" ht="27" spans="1:2">
+    <row r="15" ht="30" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
@@ -5131,7 +5161,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" ht="40.5" spans="1:2">
+    <row r="17" ht="45" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
@@ -5155,7 +5185,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" ht="27" spans="1:1">
+    <row r="20" ht="30" spans="1:1">
       <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
@@ -5168,7 +5198,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" ht="27" spans="1:2">
+    <row r="22" ht="30" spans="1:2">
       <c r="A22" s="2" t="s">
         <v>38</v>
       </c>
@@ -5176,7 +5206,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" ht="40.5" spans="1:2">
+    <row r="23" ht="43.5" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>40</v>
       </c>
@@ -5184,7 +5214,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" ht="27" spans="1:2">
+    <row r="24" ht="30" spans="1:2">
       <c r="A24" s="2" t="s">
         <v>42</v>
       </c>
@@ -5192,7 +5222,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" ht="27" spans="1:2">
+    <row r="25" ht="30" spans="1:2">
       <c r="A25" s="2" t="s">
         <v>43</v>
       </c>
@@ -5208,12 +5238,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" ht="27" spans="1:1">
+    <row r="27" ht="30" spans="1:1">
       <c r="A27" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="28" ht="27" spans="1:2">
+    <row r="28" ht="30" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>48</v>
       </c>
@@ -5221,7 +5251,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" ht="27" spans="1:2">
+    <row r="29" ht="30" spans="1:2">
       <c r="A29" s="3" t="s">
         <v>49</v>
       </c>
@@ -5237,7 +5267,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" ht="27" spans="1:2">
+    <row r="31" ht="30" spans="1:2">
       <c r="A31" s="3" t="s">
         <v>53</v>
       </c>
@@ -5245,7 +5275,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" ht="27" spans="1:2">
+    <row r="32" ht="30" spans="1:2">
       <c r="A32" s="3" t="s">
         <v>55</v>
       </c>
@@ -5253,7 +5283,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" ht="27" spans="1:2">
+    <row r="33" ht="30" spans="1:2">
       <c r="A33" s="3" t="s">
         <v>57</v>
       </c>
@@ -5261,7 +5291,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" ht="27" spans="1:2">
+    <row r="34" ht="30" spans="1:2">
       <c r="A34" s="3" t="s">
         <v>59</v>
       </c>
@@ -5285,7 +5315,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" ht="27" spans="1:2">
+    <row r="37" ht="30" spans="1:2">
       <c r="A37" s="3" t="s">
         <v>64</v>
       </c>
@@ -5293,7 +5323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" ht="27" spans="1:2">
+    <row r="38" ht="30" spans="1:2">
       <c r="A38" s="3" t="s">
         <v>66</v>
       </c>
@@ -5301,7 +5331,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" ht="27" spans="1:2">
+    <row r="39" ht="30" spans="1:2">
       <c r="A39" s="3" t="s">
         <v>68</v>
       </c>
@@ -5317,7 +5347,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" ht="30" spans="1:2">
       <c r="A41" s="3" t="s">
         <v>72</v>
       </c>
@@ -5325,7 +5355,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="42" ht="27" spans="1:2">
+    <row r="42" ht="30" spans="1:2">
       <c r="A42" s="3" t="s">
         <v>74</v>
       </c>
@@ -5333,7 +5363,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" ht="27" spans="1:2">
+    <row r="43" ht="30" spans="1:2">
       <c r="A43" s="3" t="s">
         <v>76</v>
       </c>
@@ -5751,15 +5781,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:G159"/>
-  <sheetFormatPr defaultColWidth="15.8833333333333" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="15.8857142857143" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="15.8833333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="43.2166666666667" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15.8857142857143" style="2" customWidth="1"/>
+    <col min="2" max="2" width="43.2190476190476" style="2" customWidth="1"/>
     <col min="3" max="3" width="42.3333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.8833333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.8857142857143" style="2" customWidth="1"/>
     <col min="5" max="5" width="32.6666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.2166666666667" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="15.8833333333333" style="2"/>
+    <col min="6" max="6" width="41.2190476190476" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="15.8857142857143" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5782,7 +5812,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" ht="54" hidden="1" spans="1:5">
+    <row r="2" ht="45" hidden="1" spans="1:5">
       <c r="A2" s="2" t="str">
         <f>D2</f>
         <v>拉姆</v>
@@ -5800,7 +5830,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" ht="40.5" hidden="1" spans="1:5">
+    <row r="3" ht="45" hidden="1" spans="1:5">
       <c r="A3" s="2" t="str">
         <f>D3</f>
         <v>白</v>
@@ -5818,7 +5848,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" ht="81" spans="1:6">
+    <row r="4" ht="75" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
@@ -5838,7 +5868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:6">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>98</v>
       </c>
@@ -5879,7 +5909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="27" spans="1:6">
+    <row r="7" ht="30" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>106</v>
       </c>
@@ -5899,7 +5929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="40.5" spans="1:6">
+    <row r="8" ht="30" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>109</v>
       </c>
@@ -5940,7 +5970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" ht="27" spans="1:6">
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="str">
         <f>D10</f>
         <v>银狼</v>
@@ -5961,7 +5991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="40.5" hidden="1" spans="1:5">
+    <row r="11" ht="30" hidden="1" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>119</v>
       </c>
@@ -5978,7 +6008,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:6">
+    <row r="12" ht="30" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>123</v>
       </c>
@@ -5998,7 +6028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="40.5" spans="1:6">
+    <row r="13" ht="30" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>127</v>
       </c>
@@ -6018,7 +6048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="67.5" hidden="1" spans="1:5">
+    <row r="14" ht="60" hidden="1" spans="1:5">
       <c r="A14" s="2" t="s">
         <v>132</v>
       </c>
@@ -6035,7 +6065,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="15" ht="27" hidden="1" spans="1:5">
+    <row r="15" ht="30" hidden="1" spans="1:5">
       <c r="A15" s="2" t="str">
         <f>D15</f>
         <v>桂乃芬</v>
@@ -6053,7 +6083,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="16" ht="27" hidden="1" spans="1:5">
+    <row r="16" hidden="1" spans="1:5">
       <c r="A16" s="2" t="str">
         <f>D16</f>
         <v>克莱因</v>
@@ -6071,7 +6101,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" ht="40.5" spans="1:6">
+    <row r="17" ht="30" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>143</v>
       </c>
@@ -6109,7 +6139,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" ht="67.5" spans="1:6">
+    <row r="19" ht="75" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>150</v>
       </c>
@@ -6129,7 +6159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="40.5" spans="1:6">
+    <row r="20" ht="30" spans="1:6">
       <c r="A20" s="2" t="str">
         <f>D20</f>
         <v>蝴蝶忍</v>
@@ -6150,7 +6180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="40.5" spans="1:6">
+    <row r="21" ht="30" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>157</v>
       </c>
@@ -6170,7 +6200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="67.5" spans="1:6">
+    <row r="22" ht="60" spans="1:6">
       <c r="A22" s="2" t="s">
         <v>161</v>
       </c>
@@ -6190,7 +6220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="54" spans="1:6">
+    <row r="23" ht="45" spans="1:6">
       <c r="A23" s="2" t="s">
         <v>166</v>
       </c>
@@ -6210,7 +6240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="54" spans="1:6">
+    <row r="24" ht="60" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>170</v>
       </c>
@@ -6382,7 +6412,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="33" ht="40.5" hidden="1" spans="1:5">
+    <row r="33" ht="45" hidden="1" spans="1:5">
       <c r="A33" s="2" t="str">
         <f t="shared" si="0"/>
         <v>乔艾莉·波妮 (Jewelry Bonney)</v>
@@ -6400,7 +6430,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" ht="27" hidden="1" spans="1:5">
+    <row r="34" ht="28.5" hidden="1" spans="1:5">
       <c r="A34" s="2" t="str">
         <f t="shared" si="0"/>
         <v>蕾贝卡（Rebecca）</v>
@@ -6459,7 +6489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="27" hidden="1" spans="1:5">
+    <row r="37" ht="30" hidden="1" spans="1:5">
       <c r="A37" s="2" t="s">
         <v>213</v>
       </c>
@@ -6496,7 +6526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="27" spans="1:6">
+    <row r="39" ht="30" spans="1:6">
       <c r="A39" s="2" t="str">
         <f>D39</f>
         <v>妮可·德玛拉 (Nicole Demara)</v>
@@ -6517,7 +6547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" ht="27" spans="1:6">
+    <row r="40" ht="30" spans="1:6">
       <c r="A40" s="2" t="str">
         <f>D40</f>
         <v>伊莲（Elaine）</v>
@@ -6559,7 +6589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="27" hidden="1" spans="1:5">
+    <row r="42" ht="30" hidden="1" spans="1:5">
       <c r="A42" s="2" t="s">
         <v>232</v>
       </c>
@@ -6576,7 +6606,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="43" ht="27" spans="1:6">
+    <row r="43" ht="30" spans="1:6">
       <c r="A43" s="2" t="str">
         <f>D43</f>
         <v>八重神子</v>
@@ -6597,7 +6627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="54" hidden="1" spans="1:5">
+    <row r="44" ht="60" hidden="1" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>239</v>
       </c>
@@ -6614,7 +6644,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="45" ht="40.5" hidden="1" spans="1:5">
+    <row r="45" ht="45" hidden="1" spans="1:5">
       <c r="A45" s="2" t="s">
         <v>243</v>
       </c>
@@ -6631,7 +6661,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="46" ht="40.5" hidden="1" spans="1:5">
+    <row r="46" ht="45" hidden="1" spans="1:5">
       <c r="A46" s="2" t="s">
         <v>247</v>
       </c>
@@ -6648,7 +6678,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="47" ht="27" spans="1:6">
+    <row r="47" spans="1:6">
       <c r="A47" s="2" t="str">
         <f>D47</f>
         <v>甘雨</v>
@@ -6669,7 +6699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" ht="27" spans="1:6">
+    <row r="48" ht="30" spans="1:6">
       <c r="A48" s="2" t="s">
         <v>252</v>
       </c>
@@ -6689,7 +6719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" ht="27" hidden="1" spans="1:5">
+    <row r="49" ht="30" hidden="1" spans="1:5">
       <c r="A49" s="2" t="s">
         <v>256</v>
       </c>
@@ -6726,7 +6756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" ht="27" hidden="1" spans="1:5">
+    <row r="51" ht="30" hidden="1" spans="1:5">
       <c r="A51" s="2" t="s">
         <v>264</v>
       </c>
@@ -6743,7 +6773,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="52" ht="40.5" hidden="1" spans="1:5">
+    <row r="52" ht="45" hidden="1" spans="1:5">
       <c r="A52" s="2" t="str">
         <f>D52</f>
         <v>罗莎莉亚</v>
@@ -6779,7 +6809,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="54" ht="54" hidden="1" spans="1:5">
+    <row r="54" ht="60" hidden="1" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>273</v>
       </c>
@@ -6796,7 +6826,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="55" ht="27" hidden="1" spans="1:5">
+    <row r="55" ht="30" hidden="1" spans="1:5">
       <c r="A55" s="2" t="s">
         <v>277</v>
       </c>
@@ -6813,7 +6843,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="56" ht="27" spans="1:6">
+    <row r="56" ht="30" spans="1:6">
       <c r="A56" s="2" t="s">
         <v>281</v>
       </c>
@@ -6833,7 +6863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" ht="40.5" hidden="1" spans="1:5">
+    <row r="57" ht="30" hidden="1" spans="1:5">
       <c r="A57" s="2" t="s">
         <v>284</v>
       </c>
@@ -6850,7 +6880,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="58" ht="40.5" hidden="1" spans="1:5">
+    <row r="58" ht="45" hidden="1" spans="1:5">
       <c r="A58" s="2" t="s">
         <v>287</v>
       </c>
@@ -6867,7 +6897,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="59" ht="40.5" spans="1:6">
+    <row r="59" ht="45" spans="1:6">
       <c r="A59" s="2" t="s">
         <v>291</v>
       </c>
@@ -6887,7 +6917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" ht="27" hidden="1" spans="1:5">
+    <row r="60" ht="30" hidden="1" spans="1:5">
       <c r="A60" s="2" t="s">
         <v>294</v>
       </c>
@@ -6904,7 +6934,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="61" ht="27" spans="1:6">
+    <row r="61" ht="30" spans="1:6">
       <c r="A61" s="2" t="str">
         <f>D61</f>
         <v>优菈·劳伦斯</v>
@@ -6945,7 +6975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" ht="54" spans="1:6">
+    <row r="63" ht="45" spans="1:6">
       <c r="A63" s="2" t="s">
         <v>305</v>
       </c>
@@ -6965,7 +6995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" ht="54" spans="1:6">
+    <row r="64" ht="60" spans="1:6">
       <c r="A64" s="2" t="s">
         <v>309</v>
       </c>
@@ -7005,7 +7035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" ht="27" hidden="1" spans="1:5">
+    <row r="66" ht="30" hidden="1" spans="1:5">
       <c r="A66" s="2" t="str">
         <f>D66</f>
         <v>宵宫</v>
@@ -7023,7 +7053,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="67" ht="27" hidden="1" spans="1:5">
+    <row r="67" hidden="1" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>319</v>
       </c>
@@ -7040,7 +7070,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="68" ht="27" spans="1:6">
+    <row r="68" ht="30" spans="1:6">
       <c r="A68" s="2" t="str">
         <f>D68</f>
         <v>辛焱</v>
@@ -7061,7 +7091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" ht="27" hidden="1" spans="1:5">
+    <row r="69" ht="30" hidden="1" spans="1:5">
       <c r="A69" s="2" t="str">
         <f>D69</f>
         <v>绮良良</v>
@@ -7079,7 +7109,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="70" ht="40.5" hidden="1" spans="1:5">
+    <row r="70" ht="45" hidden="1" spans="1:5">
       <c r="A70" s="2" t="s">
         <v>329</v>
       </c>
@@ -7096,7 +7126,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="71" ht="27" hidden="1" spans="1:5">
+    <row r="71" ht="30" hidden="1" spans="1:5">
       <c r="A71" s="2" t="s">
         <v>333</v>
       </c>
@@ -7134,7 +7164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" ht="27" hidden="1" spans="1:5">
+    <row r="73" ht="30" hidden="1" spans="1:5">
       <c r="A73" s="2" t="str">
         <f>D73</f>
         <v>娜维娅</v>
@@ -7152,7 +7182,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="74" ht="27" hidden="1" spans="1:5">
+    <row r="74" ht="30" hidden="1" spans="1:5">
       <c r="A74" s="2" t="str">
         <f>D74</f>
         <v>宵宫</v>
@@ -7170,7 +7200,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="75" ht="27" spans="1:6">
+    <row r="75" ht="30" spans="1:6">
       <c r="A75" s="2" t="s">
         <v>345</v>
       </c>
@@ -7190,7 +7220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" ht="27" spans="1:6">
+    <row r="76" ht="30" spans="1:6">
       <c r="A76" s="2" t="str">
         <f>D76</f>
         <v>纳西妲</v>
@@ -7229,7 +7259,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="78" ht="27" hidden="1" spans="1:5">
+    <row r="78" ht="30" hidden="1" spans="1:5">
       <c r="A78" s="2" t="str">
         <f>D78</f>
         <v>Clorinde</v>
@@ -7268,7 +7298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" ht="28.5" spans="1:6">
       <c r="A80" s="2" t="s">
         <v>359</v>
       </c>
@@ -7288,7 +7318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" ht="27" hidden="1" spans="1:5">
+    <row r="81" ht="30" hidden="1" spans="1:5">
       <c r="A81" s="2" t="s">
         <v>363</v>
       </c>
@@ -7305,7 +7335,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="82" ht="27" hidden="1" spans="1:5">
+    <row r="82" ht="30" hidden="1" spans="1:5">
       <c r="A82" s="2" t="s">
         <v>368</v>
       </c>
@@ -7322,7 +7352,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="83" ht="40.5" hidden="1" spans="1:5">
+    <row r="83" ht="45" hidden="1" spans="1:5">
       <c r="A83" s="2" t="s">
         <v>373</v>
       </c>
@@ -7339,7 +7369,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="84" ht="27" hidden="1" spans="1:5">
+    <row r="84" ht="30" hidden="1" spans="1:5">
       <c r="A84" s="2" t="str">
         <f>D84</f>
         <v>佩罗娜（Perona）</v>
@@ -7357,7 +7387,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="85" ht="27" hidden="1" spans="1:5">
+    <row r="85" ht="30" hidden="1" spans="1:5">
       <c r="A85" s="2" t="s">
         <v>382</v>
       </c>
@@ -7391,7 +7421,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="87" ht="54" hidden="1" spans="1:5">
+    <row r="87" ht="45" hidden="1" spans="1:5">
       <c r="A87" s="2" t="s">
         <v>392</v>
       </c>
@@ -7408,7 +7438,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="88" ht="40.5" hidden="1" spans="1:5">
+    <row r="88" ht="45" hidden="1" spans="1:5">
       <c r="A88" s="2" t="s">
         <v>396</v>
       </c>
@@ -7425,7 +7455,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="89" ht="27" spans="1:6">
+    <row r="89" ht="30" spans="1:6">
       <c r="A89" s="2" t="s">
         <v>401</v>
       </c>
@@ -7445,7 +7475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" ht="40.5" hidden="1" spans="1:5">
+    <row r="90" ht="45" hidden="1" spans="1:5">
       <c r="A90" s="2" t="s">
         <v>406</v>
       </c>
@@ -7462,7 +7492,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="91" ht="27" hidden="1" spans="1:5">
+    <row r="91" ht="30" hidden="1" spans="1:5">
       <c r="A91" s="2" t="s">
         <v>410</v>
       </c>
@@ -7479,7 +7509,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="92" ht="40.5" hidden="1" spans="1:5">
+    <row r="92" ht="45" hidden="1" spans="1:5">
       <c r="A92" s="2" t="str">
         <f>D92</f>
         <v>芙蕾雅</v>
@@ -7515,7 +7545,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="94" ht="54" hidden="1" spans="1:5">
+    <row r="94" ht="60" hidden="1" spans="1:5">
       <c r="A94" s="2" t="s">
         <v>422</v>
       </c>
@@ -7549,7 +7579,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="96" ht="27" hidden="1" spans="1:5">
+    <row r="96" hidden="1" spans="1:5">
       <c r="A96" s="2" t="str">
         <f>D96</f>
         <v>Barghest</v>
@@ -7585,7 +7615,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="98" ht="27" hidden="1" spans="1:5">
+    <row r="98" ht="30" hidden="1" spans="1:5">
       <c r="A98" s="2" t="s">
         <v>436</v>
       </c>
@@ -7602,7 +7632,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="99" ht="54" hidden="1" spans="1:5">
+    <row r="99" ht="45" hidden="1" spans="1:5">
       <c r="A99" s="2" t="str">
         <f>D99</f>
         <v>贞德·Alter（黑贞德）</v>
@@ -7674,7 +7704,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="103" ht="67.5" hidden="1" spans="1:5">
+    <row r="103" ht="75" hidden="1" spans="1:5">
       <c r="A103" s="2" t="s">
         <v>457</v>
       </c>
@@ -7691,7 +7721,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="104" ht="27" hidden="1" spans="1:5">
+    <row r="104" ht="30" hidden="1" spans="1:5">
       <c r="A104" s="2" t="str">
         <f>D104</f>
         <v>黑魔女</v>
@@ -7727,7 +7757,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="106" ht="27" hidden="1" spans="1:5">
+    <row r="106" hidden="1" spans="1:5">
       <c r="A106" s="2" t="str">
         <f>D106</f>
         <v>布莱默顿</v>
@@ -7745,7 +7775,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="107" ht="27" hidden="1" spans="1:5">
+    <row r="107" ht="30" hidden="1" spans="1:5">
       <c r="A107" s="2" t="s">
         <v>474</v>
       </c>
@@ -7762,7 +7792,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="108" ht="67.5" hidden="1" spans="1:5">
+    <row r="108" ht="60" hidden="1" spans="1:5">
       <c r="A108" s="2" t="s">
         <v>477</v>
       </c>
@@ -7779,7 +7809,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="109" ht="27" hidden="1" spans="1:5">
+    <row r="109" ht="30" hidden="1" spans="1:5">
       <c r="A109" s="2" t="str">
         <f>D109</f>
         <v>Implacable</v>
@@ -7797,7 +7827,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="110" ht="27" hidden="1" spans="1:5">
+    <row r="110" ht="30" hidden="1" spans="1:5">
       <c r="A110" s="2" t="s">
         <v>485</v>
       </c>
@@ -7814,7 +7844,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="111" ht="67.5" hidden="1" spans="1:5">
+    <row r="111" ht="60" hidden="1" spans="1:5">
       <c r="A111" s="2" t="s">
         <v>490</v>
       </c>
@@ -7849,7 +7879,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="113" ht="27" hidden="1" spans="1:5">
+    <row r="113" ht="30" hidden="1" spans="1:5">
       <c r="A113" s="2" t="str">
         <f>D113</f>
         <v>C.C.</v>
@@ -7867,7 +7897,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="114" ht="27" hidden="1" spans="1:5">
+    <row r="114" ht="30" hidden="1" spans="1:5">
       <c r="A114" s="2" t="s">
         <v>503</v>
       </c>
@@ -7920,7 +7950,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="117" ht="40.5" hidden="1" spans="1:5">
+    <row r="117" ht="30" hidden="1" spans="1:5">
       <c r="A117" s="2" t="str">
         <f>D117</f>
         <v>韩二里（Juri Han）</v>
@@ -7938,7 +7968,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="118" ht="27" hidden="1" spans="1:5">
+    <row r="118" hidden="1" spans="1:5">
       <c r="A118" s="2" t="str">
         <f>D118</f>
         <v>罗莎</v>
@@ -7973,7 +8003,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="120" ht="27" hidden="1" spans="1:5">
+    <row r="120" hidden="1" spans="1:5">
       <c r="A120" s="2" t="s">
         <v>529</v>
       </c>
@@ -7990,7 +8020,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="121" ht="40.5" hidden="1" spans="1:5">
+    <row r="121" ht="45" hidden="1" spans="1:5">
       <c r="A121" s="2" t="s">
         <v>533</v>
       </c>
@@ -8007,7 +8037,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="122" ht="27" hidden="1" spans="1:5">
+    <row r="122" ht="30" hidden="1" spans="1:5">
       <c r="A122" s="2" t="str">
         <f>D122</f>
         <v>11号</v>
@@ -8025,7 +8055,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="123" ht="40.5" hidden="1" spans="1:5">
+    <row r="123" ht="45" hidden="1" spans="1:5">
       <c r="A123" s="2" t="str">
         <f>D123</f>
         <v>苏茜</v>
@@ -8043,7 +8073,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="124" ht="27" hidden="1" spans="1:5">
+    <row r="124" ht="30" hidden="1" spans="1:5">
       <c r="A124" s="2" t="s">
         <v>543</v>
       </c>
@@ -8060,7 +8090,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="125" ht="81" hidden="1" spans="1:5">
+    <row r="125" ht="75" hidden="1" spans="1:5">
       <c r="A125" s="2" t="str">
         <f>D125</f>
         <v>朝比奈实玖瑠</v>
@@ -8078,7 +8108,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="126" ht="27" hidden="1" spans="1:5">
+    <row r="126" ht="30" hidden="1" spans="1:5">
       <c r="A126" s="2" t="str">
         <f>D126</f>
         <v>琪琪</v>
@@ -8096,7 +8126,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="127" ht="27" hidden="1" spans="1:5">
+    <row r="127" ht="30" hidden="1" spans="1:5">
       <c r="A127" s="2" t="s">
         <v>555</v>
       </c>
@@ -8113,7 +8143,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="128" ht="27" hidden="1" spans="1:5">
+    <row r="128" hidden="1" spans="1:5">
       <c r="A128" s="2" t="s">
         <v>559</v>
       </c>
@@ -8130,7 +8160,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="129" ht="40.5" hidden="1" spans="1:5">
+    <row r="129" ht="45" hidden="1" spans="1:5">
       <c r="A129" s="2" t="str">
         <f>D129</f>
         <v>人造人18号</v>
@@ -8148,7 +8178,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="130" ht="27" hidden="1" spans="1:7">
+    <row r="130" ht="30" hidden="1" spans="1:7">
       <c r="A130" s="2" t="s">
         <v>568</v>
       </c>
@@ -8164,12 +8194,11 @@
       <c r="E130" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F130" s="2"/>
       <c r="G130" s="2" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="131" ht="27" hidden="1" spans="1:5">
+    <row r="131" ht="30" hidden="1" spans="1:5">
       <c r="A131" s="2" t="str">
         <f>D131</f>
         <v>木野真琴</v>
@@ -8187,7 +8216,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="132" ht="27" spans="1:6">
+    <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
         <v>577</v>
       </c>
@@ -8207,7 +8236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" ht="27" hidden="1" spans="1:5">
+    <row r="133" ht="30" hidden="1" spans="1:5">
       <c r="A133" s="2" t="str">
         <f t="shared" ref="A133:A139" si="1">D133</f>
         <v>阿尼丝·亚尔斯提亚</v>
@@ -8225,7 +8254,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="134" ht="27" hidden="1" spans="1:5">
+    <row r="134" ht="30" hidden="1" spans="1:5">
       <c r="A134" s="2" t="str">
         <f t="shared" si="1"/>
         <v>寒鸦</v>
@@ -8261,7 +8290,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="136" ht="40.5" hidden="1" spans="1:5">
+    <row r="136" ht="45" hidden="1" spans="1:5">
       <c r="A136" s="2" t="str">
         <f t="shared" si="1"/>
         <v>殷霖</v>
@@ -8279,7 +8308,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="137" ht="27" hidden="1" spans="1:5">
+    <row r="137" ht="30" hidden="1" spans="1:5">
       <c r="A137" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2B</v>
@@ -8297,7 +8326,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="138" ht="27" hidden="1" spans="1:5">
+    <row r="138" ht="28.5" hidden="1" spans="1:5">
       <c r="A138" s="2" t="str">
         <f t="shared" si="1"/>
         <v>伊丽莎白·里昂妮丝</v>
@@ -8315,7 +8344,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="139" ht="67.5" hidden="1" spans="1:5">
+    <row r="139" ht="60" hidden="1" spans="1:5">
       <c r="A139" s="2" t="str">
         <f t="shared" si="1"/>
         <v>琳妮特·毕晓普</v>
@@ -8333,7 +8362,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="140" ht="40.5" hidden="1" spans="1:5">
+    <row r="140" ht="30" hidden="1" spans="1:5">
       <c r="A140" s="2" t="s">
         <v>609</v>
       </c>
@@ -8386,7 +8415,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="143" ht="27" hidden="1" spans="1:5">
+    <row r="143" ht="30" hidden="1" spans="1:5">
       <c r="A143" s="2" t="str">
         <f>D143</f>
         <v>陶琪</v>
@@ -8440,7 +8469,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="146" ht="40.5" hidden="1" spans="1:5">
+    <row r="146" ht="45" hidden="1" spans="1:5">
       <c r="A146" s="2" t="s">
         <v>634</v>
       </c>
@@ -8457,7 +8486,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="147" ht="27" hidden="1" spans="1:5">
+    <row r="147" ht="30" hidden="1" spans="1:5">
       <c r="A147" s="2" t="s">
         <v>639</v>
       </c>
@@ -8474,7 +8503,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="1:5">
+    <row r="148" ht="28.5" hidden="1" spans="1:5">
       <c r="A148" s="2" t="s">
         <v>644</v>
       </c>
@@ -8491,7 +8520,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="149" ht="27" hidden="1" spans="1:5">
+    <row r="149" ht="30" hidden="1" spans="1:5">
       <c r="A149" s="2" t="str">
         <f>D149</f>
         <v>地狱的吹雪</v>
@@ -8509,7 +8538,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="150" ht="27" hidden="1" spans="1:5">
+    <row r="150" hidden="1" spans="1:5">
       <c r="A150" s="2" t="s">
         <v>653</v>
       </c>
@@ -8543,7 +8572,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="152" hidden="1" spans="1:5">
+    <row r="152" ht="27" hidden="1" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>663</v>
       </c>
@@ -8560,7 +8589,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="153" ht="27" hidden="1" spans="1:5">
+    <row r="153" ht="30" hidden="1" spans="1:5">
       <c r="A153" s="2" t="str">
         <f>D153</f>
         <v>蒂法·洛克哈特</v>
@@ -8598,7 +8627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" ht="27" spans="1:6">
+    <row r="155" spans="1:6">
       <c r="A155" s="2" t="s">
         <v>676</v>
       </c>
@@ -8618,7 +8647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" ht="27" spans="1:6">
+    <row r="156" ht="30" spans="1:6">
       <c r="A156" s="2" t="s">
         <v>679</v>
       </c>
@@ -8638,7 +8667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" ht="27" spans="1:6">
+    <row r="157" spans="1:6">
       <c r="A157" s="2" t="s">
         <v>683</v>
       </c>
@@ -8678,7 +8707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" ht="27" spans="1:6">
+    <row r="159" spans="1:6">
       <c r="A159" s="2" t="s">
         <v>689</v>
       </c>
@@ -8699,7 +8728,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G159" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:G159">
     <filterColumn colId="5">
       <customFilters>
         <customFilter operator="equal" val="1"/>
@@ -8752,13 +8781,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="20.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="49.75" style="2" customWidth="1"/>
-    <col min="4" max="6" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="2" width="20.247619047619" style="2" customWidth="1"/>
+    <col min="3" max="3" width="68.7142857142857" style="2" customWidth="1"/>
+    <col min="4" max="6" width="20.247619047619" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -8782,18 +8811,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:6">
+    <row r="2" ht="60" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>692</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>97</v>
@@ -8802,98 +8831,88 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:6">
+    <row r="3" ht="60" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="40.5" spans="1:6">
+    <row r="4" ht="30" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:6">
+    <row r="5" hidden="1" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>698</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
         <v>699</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="40.5" spans="1:6">
+    </row>
+    <row r="6" hidden="1" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>701</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="27" spans="1:6">
+    </row>
+    <row r="7" ht="30" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>105</v>
@@ -8902,118 +8921,93 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="27" spans="1:6">
+    <row r="8" hidden="1" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>704</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="27" spans="1:6">
+    </row>
+    <row r="9" hidden="1" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>706</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="27" spans="1:6">
+    </row>
+    <row r="10" hidden="1" spans="1:5">
       <c r="A10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" ht="30" hidden="1" spans="1:5">
+      <c r="A11" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" hidden="1" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" ht="75" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="27" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="40.5" spans="1:6">
-      <c r="A12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="54" spans="1:6">
-      <c r="A13" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>153</v>
@@ -9022,18 +9016,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="27" spans="1:6">
+    <row r="14" ht="75" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>153</v>
@@ -9042,50 +9036,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="27" spans="1:6">
+    <row r="15" ht="45" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" hidden="1" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>713</v>
+      </c>
       <c r="D16" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" ht="30" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>715</v>
+      </c>
       <c r="D17" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>165</v>
@@ -9094,78 +9091,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" hidden="1" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+        <v>170</v>
+      </c>
       <c r="D18" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+    </row>
+    <row r="19" hidden="1" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+        <v>176</v>
+      </c>
       <c r="D19" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" hidden="1" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+        <v>179</v>
+      </c>
       <c r="D20" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" hidden="1" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+        <v>185</v>
+      </c>
       <c r="D21" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" ht="30" spans="1:6">
+      <c r="A22" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>717</v>
+      </c>
       <c r="D22" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>209</v>
@@ -9174,78 +9155,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" hidden="1" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+        <v>212</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="27" spans="1:6">
+    </row>
+    <row r="24" hidden="1" spans="1:5">
       <c r="A24" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="25" ht="30" hidden="1" spans="1:5">
+      <c r="A25" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F24" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+    </row>
+    <row r="26" hidden="1" spans="1:5">
       <c r="A26" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="27" ht="45" spans="1:6">
+      <c r="A27" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2" t="s">
+      <c r="B27" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>231</v>
@@ -9254,14 +9219,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" ht="30" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>720</v>
+      </c>
       <c r="D28" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>231</v>
@@ -9270,14 +9239,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" ht="30" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>721</v>
+      </c>
       <c r="D29" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>231</v>
@@ -9286,14 +9259,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" ht="45" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>722</v>
+      </c>
       <c r="D30" s="2" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>231</v>
@@ -9302,46 +9279,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" hidden="1" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
+        <v>260</v>
+      </c>
       <c r="D31" s="2" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+    </row>
+    <row r="32" hidden="1" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+        <v>281</v>
+      </c>
       <c r="D32" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+    </row>
+    <row r="33" ht="45" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>723</v>
+      </c>
       <c r="D33" s="2" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>231</v>
@@ -9350,30 +9321,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" hidden="1" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+        <v>300</v>
+      </c>
       <c r="D34" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F34" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+    </row>
+    <row r="35" ht="30" spans="1:6">
       <c r="A35" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>724</v>
+      </c>
       <c r="D35" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>231</v>
@@ -9382,30 +9352,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" hidden="1" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
+        <v>305</v>
+      </c>
       <c r="D36" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F36" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+    </row>
+    <row r="37" ht="30" spans="1:6">
       <c r="A37" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>725</v>
+      </c>
       <c r="D37" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>231</v>
@@ -9414,14 +9383,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" ht="30" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>726</v>
+      </c>
       <c r="D38" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>231</v>
@@ -9430,62 +9403,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" hidden="1" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
+        <v>325</v>
+      </c>
       <c r="D39" s="2" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F39" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+    </row>
+    <row r="40" hidden="1" spans="1:5">
       <c r="A40" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
+        <v>339</v>
+      </c>
       <c r="D40" s="2" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F40" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+    </row>
+    <row r="41" hidden="1" spans="1:5">
       <c r="A41" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
+        <v>345</v>
+      </c>
       <c r="D41" s="2" t="s">
-        <v>350</v>
+        <v>308</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F41" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+    </row>
+    <row r="42" ht="30" spans="1:6">
       <c r="A42" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>727</v>
+      </c>
       <c r="D42" s="2" t="s">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>231</v>
@@ -9494,18 +9456,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="40.5" spans="1:6">
+    <row r="43" ht="45" spans="1:6">
       <c r="A43" s="2" t="s">
-        <v>359</v>
+        <v>280</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>362</v>
+        <v>280</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>231</v>
@@ -9514,142 +9476,165 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="27" spans="1:6">
+    <row r="44" hidden="1" spans="1:5">
       <c r="A44" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" ht="43.5" hidden="1" spans="1:5">
+      <c r="A45" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="F44" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="2" t="s">
+    </row>
+    <row r="46" hidden="1" spans="1:5">
+      <c r="A46" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F45" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="2" t="s">
+    </row>
+    <row r="47" hidden="1" spans="1:5">
+      <c r="A47" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2" t="s">
-        <v>676</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="F47" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+    </row>
+    <row r="48" hidden="1" spans="1:5">
       <c r="A48" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
+        <v>676</v>
+      </c>
       <c r="D48" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="F48" s="2">
+    </row>
+    <row r="49" hidden="1" spans="1:5">
+      <c r="A49" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:5">
+      <c r="A50" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" spans="1:5">
+      <c r="A51" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" spans="1:5">
+      <c r="A52" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53" ht="30" spans="1:6">
+      <c r="A53" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F53" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F49" s="2">
+    <row r="54" ht="75" spans="1:6">
+      <c r="A54" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="F54" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F50" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F51" s="2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B4">
+  <autoFilter ref="A1:F54">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
+  <conditionalFormatting sqref="B10">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9661,7 +9646,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C143"/>
-  <sheetFormatPr defaultColWidth="64" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="64" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="64" style="2" customWidth="1"/>
     <col min="2" max="16384" width="64" style="2"/>
@@ -9669,138 +9654,138 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>723</v>
+        <v>737</v>
       </c>
     </row>
     <row r="2" spans="2:2">
       <c r="B2" s="2" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="5" ht="27" spans="1:2">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>729</v>
+        <v>743</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="7" ht="27" spans="1:2">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="7" ht="30" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>732</v>
+        <v>746</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>733</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>734</v>
+        <v>748</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="9" ht="27" spans="1:2">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="9" ht="30" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>736</v>
+        <v>750</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>737</v>
+        <v>751</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>738</v>
+        <v>752</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>739</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>741</v>
+        <v>755</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>742</v>
+        <v>756</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>743</v>
+        <v>757</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>744</v>
+        <v>758</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>745</v>
+        <v>759</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>747</v>
+        <v>761</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>749</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="7" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>754</v>
+        <v>768</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -10317,665 +10302,665 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C143"/>
-  <sheetFormatPr defaultColWidth="15.8833333333333" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="15.8857142857143" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="47.8833333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="28.8833333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.8833333333333" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="15.8833333333333" style="2"/>
+    <col min="1" max="1" width="47.8857142857143" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.8857142857143" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.8857142857143" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="15.8857142857143" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>755</v>
+        <v>769</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
     </row>
     <row r="2" spans="2:2">
       <c r="B2" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="3" ht="27" spans="1:2">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>757</v>
+        <v>771</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="4" ht="27" spans="1:2">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="4" ht="30" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>759</v>
+        <v>773</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="5" ht="27" spans="1:2">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="5" ht="30" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>761</v>
+        <v>775</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>762</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>763</v>
+        <v>777</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="7" ht="27" spans="1:2">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="7" ht="30" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>766</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>768</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>770</v>
+        <v>784</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>771</v>
+        <v>785</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="11" ht="27" spans="1:2">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="11" ht="30" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="12" ht="40.5" spans="1:2">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="12" ht="30" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="14" ht="27" spans="1:2">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="16" ht="27" spans="1:2">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="16" ht="30" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>798</v>
+        <v>812</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="25" ht="27" spans="1:2">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>800</v>
+        <v>814</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>801</v>
+        <v>815</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>803</v>
+        <v>817</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>805</v>
+        <v>819</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>806</v>
+        <v>820</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="29" ht="40.5" spans="1:2">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="29" ht="45" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>808</v>
+        <v>822</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>810</v>
+        <v>824</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="31" ht="40.5" spans="1:2">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="31" ht="45" spans="1:2">
       <c r="A31" s="2" t="s">
-        <v>812</v>
+        <v>826</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="32" ht="40.5" spans="1:2">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="32" ht="30" spans="1:2">
       <c r="A32" s="2" t="s">
-        <v>814</v>
+        <v>828</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>815</v>
+        <v>829</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>818</v>
+        <v>832</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="35" ht="27" spans="1:2">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="2" t="s">
-        <v>820</v>
+        <v>834</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>821</v>
+        <v>835</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2" t="s">
-        <v>822</v>
+        <v>836</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>823</v>
+        <v>837</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2" t="s">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>824</v>
+        <v>838</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2" t="s">
-        <v>825</v>
+        <v>839</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="39" ht="27" spans="1:2">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="2" t="s">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="40" ht="27" spans="1:2">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="40" ht="30" spans="1:2">
       <c r="A40" s="2" t="s">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>830</v>
+        <v>844</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2" t="s">
-        <v>831</v>
+        <v>845</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>832</v>
+        <v>846</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2" t="s">
-        <v>833</v>
+        <v>847</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>834</v>
+        <v>848</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2" t="s">
-        <v>835</v>
+        <v>849</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>836</v>
+        <v>850</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="45" ht="40.5" spans="1:2">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="45" ht="30" spans="1:2">
       <c r="A45" s="2" t="s">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="46" ht="27" spans="1:2">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="46" ht="30" spans="1:2">
       <c r="A46" s="2" t="s">
-        <v>841</v>
+        <v>855</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="47" ht="67.5" spans="1:2">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="47" ht="60" spans="1:2">
       <c r="A47" s="2" t="s">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="48" ht="67.5" spans="1:2">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="48" ht="75" spans="1:2">
       <c r="A48" s="2" t="s">
-        <v>845</v>
+        <v>859</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="49" ht="40.5" spans="1:2">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="49" ht="45" spans="1:2">
       <c r="A49" s="2" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>851</v>
+        <v>865</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="52" ht="27" spans="1:2">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="52" ht="30" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>853</v>
+        <v>867</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>854</v>
+        <v>868</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="54" ht="27" spans="1:2">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="54" ht="30" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>857</v>
+        <v>871</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>858</v>
+        <v>872</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2" t="s">
-        <v>859</v>
+        <v>873</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="56" ht="40.5" spans="1:2">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="56" ht="30" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>861</v>
+        <v>875</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="57" ht="27" spans="1:2">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="57" ht="30" spans="1:2">
       <c r="A57" s="2" t="s">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="58" ht="54" spans="1:2">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="58" ht="45" spans="1:2">
       <c r="A58" s="2" t="s">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="59" ht="27" spans="1:2">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="59" ht="30" spans="1:2">
       <c r="A59" s="2" t="s">
-        <v>867</v>
+        <v>881</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>868</v>
+        <v>882</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="6" t="s">
-        <v>869</v>
+        <v>883</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="61" ht="27" spans="1:2">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="61" ht="30" spans="1:2">
       <c r="A61" s="6" t="s">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="62" ht="67.5" spans="1:2">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="62" ht="75" spans="1:2">
       <c r="A62" s="6" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>874</v>
+        <v>888</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="6" t="s">
-        <v>875</v>
+        <v>889</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="64" ht="27" spans="1:2">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="6" t="s">
-        <v>877</v>
+        <v>891</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="65" ht="108" spans="1:3">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="65" ht="90" spans="1:3">
       <c r="A65" s="6" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>881</v>
+        <v>895</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="6" t="s">
-        <v>882</v>
+        <v>896</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>883</v>
+        <v>897</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="6" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="68" ht="27" spans="1:2">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" s="6" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="69" ht="27" spans="1:3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="69" ht="30" spans="1:3">
       <c r="A69" s="6" t="s">
-        <v>887</v>
+        <v>901</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>888</v>
+        <v>902</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="70" ht="81" spans="1:2">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="70" ht="90" spans="1:2">
       <c r="A70" s="6" t="s">
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="71" ht="40.5" spans="1:2">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="71" ht="30" spans="1:2">
       <c r="A71" s="6" t="s">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="72" ht="40.5" spans="1:2">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="72" ht="30" spans="1:2">
       <c r="A72" s="6" t="s">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>895</v>
+        <v>909</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="6" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>897</v>
+        <v>911</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="74" ht="27" spans="1:3">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="74" ht="30" spans="1:3">
       <c r="A74" s="6" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>900</v>
+        <v>914</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="75" ht="27" spans="1:3">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="75" ht="30" spans="1:3">
       <c r="A75" s="6" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>903</v>
+        <v>917</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="76" ht="54" spans="1:3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="76" ht="45" spans="1:3">
       <c r="A76" s="6" t="s">
-        <v>905</v>
+        <v>919</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="77" ht="27" spans="1:2">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="77" ht="30" spans="1:2">
       <c r="A77" s="6" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="78" ht="27" spans="1:3">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="78" ht="30" spans="1:3">
       <c r="A78" s="6" t="s">
-        <v>910</v>
+        <v>924</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>911</v>
+        <v>925</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>912</v>
+        <v>926</v>
       </c>
     </row>
     <row r="79" ht="135" spans="1:3">
       <c r="A79" s="6" t="s">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>914</v>
+        <v>928</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>915</v>
+        <v>929</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -11244,629 +11229,629 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D142"/>
-  <sheetFormatPr defaultColWidth="37.2166666666667" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="37.2190476190476" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="37.2166666666667" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="37.2166666666667" style="2"/>
+    <col min="1" max="1" width="37.2190476190476" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="37.2190476190476" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>916</v>
+        <v>930</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>917</v>
+        <v>931</v>
       </c>
     </row>
     <row r="2" spans="2:2">
       <c r="B2" s="2" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="3" ht="27" spans="1:2">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>918</v>
+        <v>932</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>743</v>
+        <v>757</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>919</v>
+        <v>933</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>920</v>
+        <v>934</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>921</v>
+        <v>935</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="6" ht="27" spans="1:2">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>923</v>
+        <v>937</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="7" ht="27" spans="1:2">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="7" ht="30" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>925</v>
+        <v>939</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>926</v>
+        <v>940</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>927</v>
+        <v>941</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="9" ht="27" spans="1:2">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>929</v>
+        <v>943</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>930</v>
+        <v>944</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>931</v>
+        <v>945</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="11" ht="27" spans="1:2">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="12" ht="40.5" spans="1:2">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="12" ht="30" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="13" ht="27" spans="1:2">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="13" ht="30" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>937</v>
+        <v>951</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="14" ht="27" spans="1:2">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>940</v>
+        <v>954</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>943</v>
+        <v>957</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="17" ht="27" spans="1:2">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="17" ht="30" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>946</v>
+        <v>960</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>947</v>
+        <v>961</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>948</v>
+        <v>962</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>949</v>
+        <v>963</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="21" ht="27" spans="1:2">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="21" ht="30" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>952</v>
+        <v>966</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="22" ht="27" spans="1:2">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="22" ht="30" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>954</v>
+        <v>968</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>955</v>
+        <v>969</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>956</v>
+        <v>970</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>957</v>
+        <v>971</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>959</v>
+        <v>973</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>960</v>
+        <v>974</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="27" ht="27" spans="1:2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>962</v>
+        <v>976</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="28" ht="27" spans="1:2">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="28" ht="30" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>964</v>
+        <v>978</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="29" ht="27" spans="1:2">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="29" ht="30" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>966</v>
+        <v>980</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="30" ht="27" spans="1:2">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="30" ht="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>968</v>
+        <v>982</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>969</v>
+        <v>983</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>741</v>
+        <v>755</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>971</v>
+        <v>985</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="33" ht="27" spans="1:2">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="33" ht="30" spans="1:2">
       <c r="A33" s="3" t="s">
-        <v>973</v>
+        <v>987</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>974</v>
+        <v>988</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="3" t="s">
-        <v>975</v>
+        <v>989</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>976</v>
+        <v>990</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>977</v>
+        <v>991</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>978</v>
+        <v>992</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="36" ht="67.5" spans="1:3">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="36" ht="75" spans="1:3">
       <c r="A36" s="3" t="s">
-        <v>980</v>
+        <v>994</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>981</v>
+        <v>995</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="37" ht="27" spans="1:3">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="37" ht="30" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>984</v>
+        <v>998</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="38" ht="27" spans="1:2">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="38" ht="30" spans="1:2">
       <c r="A38" s="3" t="s">
-        <v>986</v>
+        <v>1000</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="39" ht="27" spans="1:2">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="39" ht="30" spans="1:2">
       <c r="A39" s="3" t="s">
-        <v>988</v>
+        <v>1002</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>989</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
-        <v>990</v>
+        <v>1004</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>991</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
-        <v>992</v>
+        <v>1006</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>993</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="3" t="s">
-        <v>994</v>
+        <v>1008</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>995</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>996</v>
+        <v>1010</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>997</v>
+        <v>1011</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="44" ht="81" spans="1:2">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="44" ht="60" spans="1:2">
       <c r="A44" s="3" t="s">
-        <v>999</v>
+        <v>1013</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="45" ht="54" spans="1:2">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="45" ht="45" spans="1:2">
       <c r="A45" s="3" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="46" ht="108" spans="1:2">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="46" ht="90" spans="1:2">
       <c r="A46" s="3" t="s">
-        <v>1003</v>
+        <v>1017</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="47" ht="40.5" spans="1:2">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="47" ht="45" spans="1:2">
       <c r="A47" s="3" t="s">
-        <v>1005</v>
+        <v>1019</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="48" ht="27" spans="1:3">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="3" t="s">
-        <v>1007</v>
+        <v>1021</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>1008</v>
+        <v>1022</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="49" ht="27" spans="1:3">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="49" ht="30" spans="1:3">
       <c r="A49" s="3" t="s">
-        <v>1010</v>
+        <v>1024</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1011</v>
+        <v>1025</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="50" ht="67.5" spans="1:3">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="50" ht="60" spans="1:3">
       <c r="A50" s="3" t="s">
-        <v>1013</v>
+        <v>1027</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>1014</v>
+        <v>1028</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="51" ht="27" spans="1:4">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="51" ht="30" spans="1:4">
       <c r="A51" s="3" t="s">
-        <v>1016</v>
+        <v>1030</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1017</v>
+        <v>1031</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>1018</v>
+        <v>1032</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1019</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="3" t="s">
-        <v>1020</v>
+        <v>1034</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>1021</v>
+        <v>1035</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="53" ht="27" spans="1:3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="53" ht="30" spans="1:3">
       <c r="A53" s="3" t="s">
-        <v>1023</v>
+        <v>1037</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1024</v>
+        <v>1038</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="54" ht="81" spans="1:3">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="54" ht="75" spans="1:3">
       <c r="A54" s="3" t="s">
-        <v>1026</v>
+        <v>1040</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>1027</v>
+        <v>1041</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="55" ht="27" spans="1:3">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="55" ht="30" spans="1:3">
       <c r="A55" s="3" t="s">
-        <v>1029</v>
+        <v>1043</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1030</v>
+        <v>1044</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="56" ht="27" spans="1:3">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="56" ht="30" spans="1:3">
       <c r="A56" s="3" t="s">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="57" ht="40.5" spans="1:3">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="57" ht="30" spans="1:3">
       <c r="A57" s="3" t="s">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1035</v>
+        <v>1049</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="58" ht="27" spans="1:3">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="58" ht="30" spans="1:3">
       <c r="A58" s="3" t="s">
-        <v>1036</v>
+        <v>1050</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>1037</v>
+        <v>1051</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1038</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>1039</v>
+        <v>1053</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="60" ht="27" spans="1:3">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="60" ht="30" spans="1:3">
       <c r="A60" s="3" t="s">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="61" ht="27" spans="1:3">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="61" ht="30" spans="1:3">
       <c r="A61" s="3" t="s">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1046</v>
+        <v>1060</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="62" ht="27" spans="1:3">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="62" ht="30" spans="1:3">
       <c r="A62" s="3" t="s">
-        <v>1048</v>
+        <v>1062</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1049</v>
+        <v>1063</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="63" ht="27" spans="1:3">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="63" ht="30" spans="1:3">
       <c r="A63" s="3" t="s">
-        <v>1051</v>
+        <v>1065</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1052</v>
+        <v>1066</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>1053</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="3" t="s">
-        <v>1054</v>
+        <v>1068</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1055</v>
+        <v>1069</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>1056</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="3" t="s">
-        <v>1057</v>
+        <v>1071</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1058</v>
+        <v>1072</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="66" ht="27" spans="1:3">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="66" ht="30" spans="1:3">
       <c r="A66" s="3" t="s">
-        <v>1060</v>
+        <v>1074</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1061</v>
+        <v>1075</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="67" ht="27" spans="1:3">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="67" ht="30" spans="1:3">
       <c r="A67" s="3" t="s">
-        <v>1062</v>
+        <v>1076</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1063</v>
+        <v>1077</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>1064</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="3" t="s">
-        <v>1065</v>
+        <v>1079</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1066</v>
+        <v>1080</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="69" ht="27" spans="1:3">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="69" ht="30" spans="1:3">
       <c r="A69" s="3" t="s">
-        <v>1068</v>
+        <v>1082</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1069</v>
+        <v>1083</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>1070</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -12175,474 +12160,474 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A2:A94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>1071</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1072</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>1073</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>1074</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1075</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>1076</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>1077</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1078</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>1079</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>1080</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>1081</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>1082</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>1083</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>1084</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>1085</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>1086</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>1087</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>1088</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>1089</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>1090</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>1091</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>1092</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>1093</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>1094</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>1095</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>1096</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>1097</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>1098</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1099</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>1100</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>1101</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>1102</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>1103</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>1104</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>1105</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1106</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>1107</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>1108</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>1109</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1110</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>1111</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>1112</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>1113</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1114</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1108</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>1115</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>1116</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>1117</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>1118</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1119</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>1120</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>1121</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>1122</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>1123</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>1105</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>1124</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>1125</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>1126</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>1127</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>1128</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>1111</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="1" t="s">
-        <v>1129</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>1130</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>1131</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>1132</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>1133</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>1134</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="1" t="s">
-        <v>1135</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>1136</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>1137</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>1138</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>1139</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>1140</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>1141</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>1142</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>1143</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>1144</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>1145</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>1146</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>1147</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>1148</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>1149</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="1" t="s">
-        <v>1150</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="1" t="s">
-        <v>1151</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>1152</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>1153</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="1" t="s">
-        <v>1154</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>1155</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>1156</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>1157</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1158</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>1159</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>1160</v>
+        <v>1174</v>
       </c>
     </row>
   </sheetData>
